--- a/ignore/alma_bat.xlsx
+++ b/ignore/alma_bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documents\GitHub\alma\ignore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D85B41-D9AD-4604-822D-A0520FD46DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8DB192-64AD-434C-A4E0-4B1FC9C43B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t>A dónde lo huido</t>
   </si>
@@ -711,7 +711,12 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">

--- a/ignore/alma_bat.xlsx
+++ b/ignore/alma_bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documents\GitHub\alma\ignore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8DB192-64AD-434C-A4E0-4B1FC9C43B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E55CB8A-2E8E-4020-B392-F0B336E3B316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
   <si>
     <t>A dónde lo huido</t>
   </si>
@@ -734,7 +734,12 @@
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">

--- a/ignore/alma_bat.xlsx
+++ b/ignore/alma_bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documents\GitHub\alma\ignore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E55CB8A-2E8E-4020-B392-F0B336E3B316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB231604-751E-4BC8-B0C2-38607FDF6A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="75">
   <si>
     <t>A dónde lo huido</t>
   </si>
@@ -314,32 +314,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="8">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -387,11 +367,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}" name="Tabla1" displayName="Tabla1" ref="A1:D36" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}" name="Tabla1" displayName="Tabla1" ref="A1:D36" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:D36" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{11DD1879-9599-4ECC-B063-27D239590F87}" name="ID" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{26B7B70A-A321-471D-894C-2EFC089D04C1}" name="Título" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{11DD1879-9599-4ECC-B063-27D239590F87}" name="ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{26B7B70A-A321-471D-894C-2EFC089D04C1}" name="Título" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{7195DF70-C752-434A-8355-02B47C5CE786}" name="Estado" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{4B0CEF65-F5ED-4511-8724-E81E853C4D06}" name="Resumen" dataDxfId="0"/>
   </tableColumns>
@@ -789,7 +769,12 @@
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -852,7 +837,12 @@
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
@@ -882,7 +872,9 @@
       <c r="C21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1022,12 +1014,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="falta">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="falta">
       <formula>NOT(ISERROR(SEARCH("falta",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:D1048576">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ignore/alma_bat.xlsx
+++ b/ignore/alma_bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documents\GitHub\alma\ignore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB231604-751E-4BC8-B0C2-38607FDF6A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3795302-D1C7-459C-8CC2-54AB8F7490B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t>A dónde lo huido</t>
   </si>
@@ -110,9 +110,6 @@
     <t>A7</t>
   </si>
   <si>
-    <t>A8</t>
-  </si>
-  <si>
     <t>A9</t>
   </si>
   <si>
@@ -261,6 +258,9 @@
   </si>
   <si>
     <t>Resumen</t>
+  </si>
+  <si>
+    <t>k</t>
   </si>
 </sst>
 </file>
@@ -654,16 +654,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -692,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -715,10 +715,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -729,10 +729,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -742,11 +742,16 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -755,7 +760,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
@@ -764,21 +769,21 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -787,16 +792,21 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -805,7 +815,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
@@ -814,7 +824,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
@@ -823,7 +833,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
@@ -832,182 +842,182 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D36" s="2"/>
     </row>

--- a/ignore/alma_bat.xlsx
+++ b/ignore/alma_bat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documents\GitHub\alma\ignore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3795302-D1C7-459C-8CC2-54AB8F7490B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D8BE63-CB78-4FF9-86BF-43E7383C1C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="76">
   <si>
     <t>A dónde lo huido</t>
   </si>
@@ -260,7 +260,10 @@
     <t>Resumen</t>
   </si>
   <si>
-    <t>k</t>
+    <t>old</t>
+  </si>
+  <si>
+    <t>A8</t>
   </si>
 </sst>
 </file>
@@ -314,12 +317,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="11">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -340,6 +360,12 @@
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -367,13 +393,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}" name="Tabla1" displayName="Tabla1" ref="A1:D36" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:D36" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{11DD1879-9599-4ECC-B063-27D239590F87}" name="ID" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{26B7B70A-A321-471D-894C-2EFC089D04C1}" name="Título" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{7195DF70-C752-434A-8355-02B47C5CE786}" name="Estado" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{4B0CEF65-F5ED-4511-8724-E81E853C4D06}" name="Resumen" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}" name="Tabla1" displayName="Tabla1" ref="A1:E36" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:E36" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{11DD1879-9599-4ECC-B063-27D239590F87}" name="ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{26B7B70A-A321-471D-894C-2EFC089D04C1}" name="Título" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{7195DF70-C752-434A-8355-02B47C5CE786}" name="Estado" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{4B0CEF65-F5ED-4511-8724-E81E853C4D06}" name="Resumen" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{8CAFF69F-6ECC-424F-BD43-2EC91F489978}" name="old" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -642,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
@@ -652,7 +679,7 @@
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -665,8 +692,11 @@
       <c r="D1" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -675,16 +705,21 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -697,17 +732,26 @@
       <c r="D4" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -720,8 +764,11 @@
       <c r="D6" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -734,8 +781,11 @@
       <c r="D7" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -748,17 +798,21 @@
       <c r="D8" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -766,8 +820,9 @@
         <v>8</v>
       </c>
       <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -780,8 +835,11 @@
       <c r="D11" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -789,8 +847,9 @@
         <v>10</v>
       </c>
       <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -803,8 +862,11 @@
       <c r="D13" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -812,8 +874,9 @@
         <v>12</v>
       </c>
       <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -821,8 +884,9 @@
         <v>13</v>
       </c>
       <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -830,8 +894,9 @@
         <v>14</v>
       </c>
       <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
@@ -839,8 +904,9 @@
         <v>15</v>
       </c>
       <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -853,8 +919,11 @@
       <c r="D18" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>40</v>
       </c>
@@ -862,8 +931,9 @@
         <v>33</v>
       </c>
       <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
@@ -871,8 +941,9 @@
         <v>34</v>
       </c>
       <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
@@ -885,8 +956,11 @@
       <c r="D21" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -894,8 +968,9 @@
         <v>36</v>
       </c>
       <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -903,8 +978,9 @@
         <v>37</v>
       </c>
       <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
@@ -912,8 +988,9 @@
         <v>38</v>
       </c>
       <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>46</v>
       </c>
@@ -921,8 +998,9 @@
         <v>39</v>
       </c>
       <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
@@ -930,8 +1008,9 @@
         <v>59</v>
       </c>
       <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
@@ -939,8 +1018,9 @@
         <v>51</v>
       </c>
       <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>62</v>
       </c>
@@ -948,8 +1028,9 @@
         <v>52</v>
       </c>
       <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>63</v>
       </c>
@@ -957,8 +1038,9 @@
         <v>53</v>
       </c>
       <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>64</v>
       </c>
@@ -966,8 +1048,9 @@
         <v>54</v>
       </c>
       <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>65</v>
       </c>
@@ -975,8 +1058,9 @@
         <v>55</v>
       </c>
       <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -984,8 +1068,9 @@
         <v>56</v>
       </c>
       <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
@@ -993,8 +1078,9 @@
         <v>57</v>
       </c>
       <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
@@ -1002,8 +1088,9 @@
         <v>60</v>
       </c>
       <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1011,8 +1098,9 @@
         <v>58</v>
       </c>
       <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -1020,16 +1108,27 @@
         <v>61</v>
       </c>
       <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="falta">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="falta">
       <formula>NOT(ISERROR(SEARCH("falta",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:D1048576">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E36">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="falta">
+      <formula>NOT(ISERROR(SEARCH("falta",E4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E36">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ignore/alma_bat.xlsx
+++ b/ignore/alma_bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documents\GitHub\alma\ignore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D8BE63-CB78-4FF9-86BF-43E7383C1C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C3E814-5A3B-4B49-A94E-6711B670D613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="75">
   <si>
     <t>A dónde lo huido</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Jimena</t>
   </si>
   <si>
-    <t>Juan y María</t>
-  </si>
-  <si>
     <t>Lagarto, lagarto</t>
   </si>
   <si>
@@ -260,10 +257,10 @@
     <t>Resumen</t>
   </si>
   <si>
-    <t>old</t>
-  </si>
-  <si>
     <t>A8</t>
+  </si>
+  <si>
+    <t>Vuelve a danzar</t>
   </si>
 </sst>
 </file>
@@ -317,30 +314,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -393,14 +367,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}" name="Tabla1" displayName="Tabla1" ref="A1:E36" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:E36" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{11DD1879-9599-4ECC-B063-27D239590F87}" name="ID" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{26B7B70A-A321-471D-894C-2EFC089D04C1}" name="Título" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{7195DF70-C752-434A-8355-02B47C5CE786}" name="Estado" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{4B0CEF65-F5ED-4511-8724-E81E853C4D06}" name="Resumen" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8CAFF69F-6ECC-424F-BD43-2EC91F489978}" name="old" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}" name="Tabla1" displayName="Tabla1" ref="A1:D36" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:D36" xr:uid="{8C7B6C35-84D0-4214-BF76-626FB3ED50C2}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{11DD1879-9599-4ECC-B063-27D239590F87}" name="ID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{26B7B70A-A321-471D-894C-2EFC089D04C1}" name="Título" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{7195DF70-C752-434A-8355-02B47C5CE786}" name="Estado" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{4B0CEF65-F5ED-4511-8724-E81E853C4D06}" name="Resumen" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -669,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
@@ -679,456 +652,409 @@
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="C21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="falta">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="falta">
       <formula>NOT(ISERROR(SEARCH("falta",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:D1048576">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E36">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="falta">
-      <formula>NOT(ISERROR(SEARCH("falta",E4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E36">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
